--- a/research/traditional_assets/database/data/estonia/estonia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_investments_asset_management.xlsx
@@ -594,16 +594,16 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>0.8333333333333335</v>
+        <v>0.7596153846153847</v>
       </c>
       <c r="J2">
-        <v>0.8333333333333335</v>
+        <v>0.7596153846153847</v>
       </c>
       <c r="K2">
-        <v>0.079</v>
+        <v>0.107</v>
       </c>
       <c r="L2">
-        <v>0.7745098039215687</v>
+        <v>1.028846153846154</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,31 +627,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="V2">
-        <v>0.001401401401401401</v>
+        <v>0.009333333333333334</v>
       </c>
       <c r="W2">
-        <v>0.02781690140845071</v>
+        <v>0.03578595317725752</v>
       </c>
       <c r="X2">
-        <v>0.04887865283753826</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="Y2">
-        <v>-0.02106175142908755</v>
+        <v>-0.04359429485215974</v>
       </c>
       <c r="Z2">
-        <v>0.03600423579244617</v>
+        <v>0.03494623655913978</v>
       </c>
       <c r="AA2">
-        <v>0.03000352982703848</v>
+        <v>0.02654569892473118</v>
       </c>
       <c r="AB2">
-        <v>0.04887865283753826</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AC2">
-        <v>-0.01887512301049978</v>
+        <v>-0.05283454910468608</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -663,7 +663,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-0.014</v>
+        <v>-0.021</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -672,16 +672,19 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.00140336808340016</v>
+        <v>-0.009421265141318977</v>
       </c>
       <c r="AK2">
-        <v>-0.004704301075268816</v>
+        <v>-0.008174386920980927</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>0</v>
+        <v>-0.027</v>
+      </c>
+      <c r="AQ2">
+        <v>-2.925925925925926</v>
       </c>
     </row>
     <row r="3">
@@ -707,16 +710,16 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.8333333333333335</v>
+        <v>0.7596153846153847</v>
       </c>
       <c r="J3">
-        <v>0.8333333333333335</v>
+        <v>0.7596153846153847</v>
       </c>
       <c r="K3">
-        <v>0.079</v>
+        <v>0.107</v>
       </c>
       <c r="L3">
-        <v>0.7745098039215687</v>
+        <v>1.028846153846154</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -740,31 +743,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="V3">
-        <v>0.001401401401401401</v>
+        <v>0.009333333333333334</v>
       </c>
       <c r="W3">
-        <v>0.02781690140845071</v>
+        <v>0.03578595317725752</v>
       </c>
       <c r="X3">
-        <v>0.04887865283753826</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="Y3">
-        <v>-0.02106175142908755</v>
+        <v>-0.04359429485215974</v>
       </c>
       <c r="Z3">
-        <v>0.03600423579244617</v>
+        <v>0.03494623655913978</v>
       </c>
       <c r="AA3">
-        <v>0.03000352982703848</v>
+        <v>0.02654569892473118</v>
       </c>
       <c r="AB3">
-        <v>0.04887865283753826</v>
+        <v>0.07938024802941726</v>
       </c>
       <c r="AC3">
-        <v>-0.01887512301049978</v>
+        <v>-0.05283454910468608</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -776,7 +779,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-0.014</v>
+        <v>-0.021</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -785,16 +788,19 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.00140336808340016</v>
+        <v>-0.009421265141318977</v>
       </c>
       <c r="AK3">
-        <v>-0.004704301075268816</v>
+        <v>-0.008174386920980927</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>-0.027</v>
+      </c>
+      <c r="AQ3">
+        <v>-2.925925925925926</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/estonia/estonia_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/estonia/estonia_investments_asset_management.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -587,23 +587,26 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.08019999999999999</v>
+      </c>
       <c r="G2">
-        <v>0</v>
+        <v>0.5764753704593326</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.5764753704593326</v>
       </c>
       <c r="I2">
-        <v>0.7596153846153847</v>
+        <v>0.5191234618085067</v>
       </c>
       <c r="J2">
-        <v>0.7596153846153847</v>
+        <v>0.5191234618085067</v>
       </c>
       <c r="K2">
-        <v>0.107</v>
+        <v>-18.377</v>
       </c>
       <c r="L2">
-        <v>1.028846153846154</v>
+        <v>-0.6790953771109715</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -612,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -621,70 +624,79 @@
         <v>0</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.021</v>
+        <v>8.350999999999999</v>
       </c>
       <c r="V2">
-        <v>0.009333333333333334</v>
+        <v>0.185495335406486</v>
       </c>
       <c r="W2">
-        <v>0.03578595317725752</v>
+        <v>-0.06468080724279071</v>
       </c>
       <c r="X2">
-        <v>0.07938024802941726</v>
+        <v>0.1097333337570566</v>
       </c>
       <c r="Y2">
-        <v>-0.04359429485215974</v>
+        <v>-0.1744141409998473</v>
       </c>
       <c r="Z2">
-        <v>0.03494623655913978</v>
+        <v>0.08303238020429014</v>
       </c>
       <c r="AA2">
-        <v>0.02654569892473118</v>
+        <v>0.03099119464528262</v>
       </c>
       <c r="AB2">
-        <v>0.07938024802941726</v>
+        <v>0.06664625473758706</v>
       </c>
       <c r="AC2">
-        <v>-0.05283454910468608</v>
+        <v>-0.03565506009230444</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>152.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>152.7</v>
       </c>
       <c r="AG2">
-        <v>-0.021</v>
+        <v>144.349</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.7723042686627554</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.5470961269750277</v>
       </c>
       <c r="AJ2">
-        <v>-0.009421265141318977</v>
+        <v>0.7622630948043237</v>
       </c>
       <c r="AK2">
-        <v>-0.008174386920980927</v>
+        <v>0.5331272460010562</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>9.360999999999999</v>
       </c>
       <c r="AM2">
-        <v>-0.027</v>
+        <v>9.275999999999998</v>
+      </c>
+      <c r="AN2">
+        <v>10.90714285714286</v>
+      </c>
+      <c r="AO2">
+        <v>1.500694370259588</v>
+      </c>
+      <c r="AP2">
+        <v>10.31064285714286</v>
       </c>
       <c r="AQ2">
-        <v>-2.925925925925926</v>
+        <v>1.514445881845623</v>
       </c>
     </row>
     <row r="3">
@@ -695,112 +707,243 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Baltic Horizon Fund (TLSE:NHCBHFFT)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Investments &amp; Asset Management</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.08019999999999999</v>
+      </c>
+      <c r="G3">
+        <v>0.5777777777777777</v>
+      </c>
+      <c r="H3">
+        <v>0.5777777777777777</v>
+      </c>
+      <c r="I3">
+        <v>0.5185185185185185</v>
+      </c>
+      <c r="J3">
+        <v>0.5185185185185185</v>
+      </c>
+      <c r="K3">
+        <v>-18.4</v>
+      </c>
+      <c r="L3">
+        <v>-0.6814814814814815</v>
+      </c>
+      <c r="M3">
+        <v>-0</v>
+      </c>
+      <c r="N3">
+        <v>-0</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>-0</v>
+      </c>
+      <c r="R3">
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>8.35</v>
+      </c>
+      <c r="V3">
+        <v>0.2002398081534772</v>
+      </c>
+      <c r="W3">
+        <v>-0.1382419233658903</v>
+      </c>
+      <c r="X3">
+        <v>0.1518875274317114</v>
+      </c>
+      <c r="Y3">
+        <v>-0.2901294507976017</v>
+      </c>
+      <c r="Z3">
+        <v>0.08350343291890888</v>
+      </c>
+      <c r="AA3">
+        <v>0.04329807632832312</v>
+      </c>
+      <c r="AB3">
+        <v>0.06571336939277228</v>
+      </c>
+      <c r="AC3">
+        <v>-0.02241529306444916</v>
+      </c>
+      <c r="AD3">
+        <v>152.7</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>152.7</v>
+      </c>
+      <c r="AG3">
+        <v>144.35</v>
+      </c>
+      <c r="AH3">
+        <v>0.7854938271604939</v>
+      </c>
+      <c r="AI3">
+        <v>0.55007204610951</v>
+      </c>
+      <c r="AJ3">
+        <v>0.7758667024993281</v>
+      </c>
+      <c r="AK3">
+        <v>0.5361188486536675</v>
+      </c>
+      <c r="AL3">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="AM3">
+        <v>9.280999999999999</v>
+      </c>
+      <c r="AN3">
+        <v>10.90714285714286</v>
+      </c>
+      <c r="AO3">
+        <v>1.495726495726496</v>
+      </c>
+      <c r="AP3">
+        <v>10.31071428571429</v>
+      </c>
+      <c r="AQ3">
+        <v>1.508458140286607</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>Investment Friends SE (WSE:IFR)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0.7596153846153847</v>
-      </c>
-      <c r="J3">
-        <v>0.7596153846153847</v>
-      </c>
-      <c r="K3">
-        <v>0.107</v>
-      </c>
-      <c r="L3">
-        <v>1.028846153846154</v>
-      </c>
-      <c r="M3">
-        <v>-0</v>
-      </c>
-      <c r="N3">
-        <v>-0</v>
-      </c>
-      <c r="O3">
-        <v>-0</v>
-      </c>
-      <c r="P3">
-        <v>-0</v>
-      </c>
-      <c r="Q3">
-        <v>-0</v>
-      </c>
-      <c r="R3">
-        <v>-0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0.021</v>
-      </c>
-      <c r="V3">
-        <v>0.009333333333333334</v>
-      </c>
-      <c r="W3">
-        <v>0.03578595317725752</v>
-      </c>
-      <c r="X3">
-        <v>0.07938024802941726</v>
-      </c>
-      <c r="Y3">
-        <v>-0.04359429485215974</v>
-      </c>
-      <c r="Z3">
-        <v>0.03494623655913978</v>
-      </c>
-      <c r="AA3">
-        <v>0.02654569892473118</v>
-      </c>
-      <c r="AB3">
-        <v>0.07938024802941726</v>
-      </c>
-      <c r="AC3">
-        <v>-0.05283454910468608</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>0</v>
-      </c>
-      <c r="AG3">
-        <v>-0.021</v>
-      </c>
-      <c r="AH3">
-        <v>0</v>
-      </c>
-      <c r="AI3">
-        <v>0</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.009421265141318977</v>
-      </c>
-      <c r="AK3">
-        <v>-0.008174386920980927</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>-0.027</v>
-      </c>
-      <c r="AQ3">
-        <v>-2.925925925925926</v>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0.7868852459016393</v>
+      </c>
+      <c r="J4">
+        <v>0.7868852459016393</v>
+      </c>
+      <c r="K4">
+        <v>0.023</v>
+      </c>
+      <c r="L4">
+        <v>0.3770491803278688</v>
+      </c>
+      <c r="M4">
+        <v>-0</v>
+      </c>
+      <c r="N4">
+        <v>-0</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>-0</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>0.001</v>
+      </c>
+      <c r="V4">
+        <v>0.0003012048192771085</v>
+      </c>
+      <c r="W4">
+        <v>0.008880308880308881</v>
+      </c>
+      <c r="X4">
+        <v>0.06757914008240185</v>
+      </c>
+      <c r="Y4">
+        <v>-0.05869883120209296</v>
+      </c>
+      <c r="Z4">
+        <v>0.02374464772284936</v>
+      </c>
+      <c r="AA4">
+        <v>0.01868431296224212</v>
+      </c>
+      <c r="AB4">
+        <v>0.06757914008240185</v>
+      </c>
+      <c r="AC4">
+        <v>-0.04889482712015973</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>0</v>
+      </c>
+      <c r="AG4">
+        <v>-0.001</v>
+      </c>
+      <c r="AH4">
+        <v>0</v>
+      </c>
+      <c r="AI4">
+        <v>0</v>
+      </c>
+      <c r="AJ4">
+        <v>-0.000301295570955107</v>
+      </c>
+      <c r="AK4">
+        <v>-0.0006626905235255136</v>
+      </c>
+      <c r="AL4">
+        <v>0.001</v>
+      </c>
+      <c r="AM4">
+        <v>-0.005</v>
+      </c>
+      <c r="AO4">
+        <v>48</v>
+      </c>
+      <c r="AQ4">
+        <v>-9.6</v>
       </c>
     </row>
   </sheetData>
